--- a/src/attributions/attributions_ig_traj_334.xlsx
+++ b/src/attributions/attributions_ig_traj_334.xlsx
@@ -999,46 +999,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2875616849447382</v>
+        <v>0.3174818907299851</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04916866915458551</v>
+        <v>-0.08043996964237994</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03508385158456093</v>
+        <v>-0.0798385507391616</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1868644542137752</v>
+        <v>0.2702578040833323</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.05703157391383253</v>
+        <v>-0.1537317277646269</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.05474712759342636</v>
+        <v>-0.1060439733989868</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,28 +1047,28 @@
         <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1206807837434192</v>
+        <v>0.1322884707037021</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.011313443801532</v>
+        <v>0.02410917408108413</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01825051592766571</v>
+        <v>-0.0664371074384409</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
@@ -1080,100 +1080,100 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.08010733531357578</v>
+        <v>0.02845262447916486</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.02626001346801477</v>
+        <v>-0.09119978002309422</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.06008994739085107</v>
+        <v>-0.05500494229666345</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.03824346145446476</v>
+        <v>0.2045165790584207</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.05476268607443499</v>
+        <v>0.009547167440459726</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.05724014632862098</v>
+        <v>0.08328491844123011</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
         <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.3910389620238957</v>
+        <v>0.3711434726903329</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.07112939969320639</v>
+        <v>-0.172900791750916</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1073347573310283</v>
+        <v>-0.1768291222455304</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.06268378662608781</v>
+        <v>0.01496278825419806</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.05419754738885168</v>
+        <v>-0.1002318025485403</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.1714044837587416</v>
+        <v>-0.03637990832353264</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,7 +1182,7 @@
         <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
@@ -1191,22 +1191,22 @@
         <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.08649940010677348</v>
+        <v>-0.03417191470213681</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0889550999153564</v>
+        <v>0.05690074955973853</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1370041981581986</v>
+        <v>0.1344285152209038</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>-0</v>
@@ -1218,25 +1218,25 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2433379336229385</v>
+        <v>0.3582489258004253</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.01027184438393714</v>
+        <v>-0.1521696587543671</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.03251334630057932</v>
+        <v>-0.05629900547630786</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1245,16 +1245,16 @@
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1046876796052372</v>
+        <v>-0.1855634688749845</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.03754056057741093</v>
+        <v>0.170302869785791</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.02053975411173858</v>
+        <v>0.01678283203814954</v>
       </c>
       <c r="CI2" t="n">
         <v>-0</v>
@@ -1266,25 +1266,25 @@
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01455135153450846</v>
+        <v>-0.08678344765942077</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.005581607112081109</v>
+        <v>0.006491088479604105</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.0551390622979059</v>
+        <v>-0.001755764784259322</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,55 +1293,55 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.09721657937454102</v>
+        <v>-0.1967831597153235</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.06877484758882475</v>
+        <v>0.1733761765861564</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.01694533492893308</v>
+        <v>0.02863929736452457</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.07871607339187257</v>
+        <v>-0.1656395651934177</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1743059842711954</v>
+        <v>0.1269545509140268</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.02729263284921977</v>
+        <v>-0.05183233928656857</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.07955516908643247</v>
+        <v>-0.1270447851805184</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.07743847770319459</v>
+        <v>0.1033136461619146</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.02356452782535355</v>
+        <v>-0.09366476709484199</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>-0</v>
@@ -1380,52 +1380,52 @@
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.03095433790678925</v>
+        <v>0.0674789164020063</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.00359314839253035</v>
+        <v>0.1267008856997744</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.03279468198343286</v>
+        <v>-0.05794359022264627</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.1004088106841932</v>
+        <v>-0.1177250429476739</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.1182146961832013</v>
+        <v>-0.2157242060631314</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.08420377560068468</v>
+        <v>0.03382243153464606</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
         <v>-0</v>
@@ -1434,22 +1434,22 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.09032191128343642</v>
+        <v>-0.1632774234244798</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.1033858545114475</v>
+        <v>0.09279914937277059</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.05326855862804486</v>
+        <v>-0.01499132650886884</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>0</v>
@@ -1461,46 +1461,46 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.09222352973821804</v>
+        <v>-0.2174304608694941</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.06610024424042325</v>
+        <v>0.1826400448146551</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.02817393609221305</v>
+        <v>0.008570448776444346</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.03166039943361013</v>
+        <v>-0.04323051590393779</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.04974388937611508</v>
+        <v>-0.07336942430568408</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.02773267283674831</v>
+        <v>0.05872872614618541</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>-0</v>
@@ -1509,22 +1509,22 @@
         <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.01216710103887034</v>
+        <v>-0.1041460430301326</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.01549477217124923</v>
+        <v>0.3042547244795304</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.09626610315252219</v>
+        <v>0.1103873551317269</v>
       </c>
       <c r="FU2" t="n">
         <v>-0</v>
@@ -1533,34 +1533,34 @@
         <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03465461288083418</v>
+        <v>-0.1521579101966604</v>
       </c>
       <c r="GA2" t="n">
         <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.03939035125205836</v>
+        <v>0.06954687595669715</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>-0</v>
@@ -1568,79 +1568,79 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.05657032922563798</v>
+        <v>-0.1086779214830233</v>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2206778831596863</v>
+        <v>0.131593495520115</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09561480608313083</v>
+        <v>-0.08255751417758661</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01606098363108681</v>
+        <v>-0.001278887402986189</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.003354584733396546</v>
+        <v>-0.1164449656477148</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1314385013453385</v>
+        <v>0.07847829537585238</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008078325747970724</v>
+        <v>-0.1409167766689388</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01553833710283954</v>
+        <v>-0.003837042238562102</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.07001644433804299</v>
+        <v>0.03691713341998697</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07221133074413989</v>
+        <v>-0.04735179210004959</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.002310894449742559</v>
+        <v>-0.08010609884092036</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.07085895905375193</v>
+        <v>0.0126434257378024</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1649,160 +1649,160 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.04648959143909299</v>
+        <v>0.1148340659786392</v>
       </c>
       <c r="AC3" t="n">
         <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.02868385689615417</v>
+        <v>-0.09375824238283577</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.03456330460362744</v>
+        <v>-0.1507109802366654</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.03072818473762002</v>
+        <v>0.003350212293540195</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0250398669655454</v>
+        <v>0.001439751415233137</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.03064233091187257</v>
+        <v>-0.06083691067259345</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.008616608852701869</v>
+        <v>-0.001085826726522154</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.03057432912094433</v>
+        <v>0.03650450707961198</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.05243546824511153</v>
+        <v>-0.1235215184890631</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3236895224119415</v>
+        <v>0.07200042768492378</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4625949160891574</v>
+        <v>-0.1048338635809919</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1622288199564272</v>
+        <v>0.01368975418771644</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.1601541056855969</v>
+        <v>-0.03572810511893427</v>
       </c>
       <c r="BD3" t="n">
         <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.03843571913849204</v>
+        <v>0.002085730621019259</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.02865996860947488</v>
+        <v>0.03016588656529439</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003662045143945404</v>
+        <v>-0.0874603879624854</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.05483007094544864</v>
+        <v>0.09621788169146368</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1129997437536668</v>
+        <v>0.02953114135769273</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.07172767879568824</v>
+        <v>0.006868283938736433</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.06525404126078567</v>
+        <v>-0.003867776820904034</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.0363501323545963</v>
+        <v>-0.05379899063754751</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1785986868610728</v>
+        <v>0.08061820635138907</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2992654950657107</v>
+        <v>-0.09501329515112049</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.01665113652191133</v>
+        <v>0.01986623658718185</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
@@ -1811,325 +1811,325 @@
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.06056997599136519</v>
+        <v>0.07082115798258028</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.06063621376526408</v>
+        <v>-0.01777513143550609</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.01199649336484932</v>
+        <v>0.08126795126576922</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.02569506237924058</v>
+        <v>0.003359200086243168</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.04094996110551728</v>
+        <v>-0.03147169449162868</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.00857098631620693</v>
+        <v>0.02821458353689861</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.1498061399593144</v>
+        <v>-0.03232417870184374</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.001366267442244579</v>
+        <v>0.005340238371986497</v>
       </c>
       <c r="CT3" t="n">
         <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0304206355430492</v>
+        <v>0.07546737146088862</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.05884604490933404</v>
+        <v>-0.04802421863849959</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.005985311065094982</v>
+        <v>0.04090456370914135</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.01662746016250794</v>
+        <v>0.0156601266679742</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08795899297189221</v>
+        <v>-0.02564863241320454</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.09067166187923929</v>
+        <v>-0.03414693266491232</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1842035181396022</v>
+        <v>0.1168004398066983</v>
       </c>
       <c r="DJ3" t="n">
         <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.04330339413785377</v>
+        <v>-0.007776101207673773</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.1354894765930943</v>
+        <v>-0.1182789015252552</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.01360973518575739</v>
+        <v>0.01806869365177161</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.100950555773172</v>
+        <v>-0.1072831239743495</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.03661743061567498</v>
+        <v>0.008831927599022056</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.02390404591798257</v>
+        <v>0.04654448601990022</v>
       </c>
       <c r="DX3" t="n">
         <v>-0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.02074295438760931</v>
+        <v>0.1374529364374344</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.1681491699055639</v>
+        <v>-0.180747256374517</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.0384671687632827</v>
+        <v>0.04126501799015434</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.01578484041914852</v>
+        <v>0.0739952756586348</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.14493288716756</v>
+        <v>-0.02247535046762625</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.03755196472211719</v>
+        <v>0.02444304202896953</v>
       </c>
       <c r="EK3" t="n">
         <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0.0755129999986843</v>
+        <v>0.06740759747101663</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.06754370628021103</v>
+        <v>0.04350072367903302</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.01835058223885087</v>
+        <v>0.09481200024804884</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.1265628898252841</v>
+        <v>0.0001301433692925912</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.1264643910053201</v>
+        <v>0.03449455699637474</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
         <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.03594638219404891</v>
+        <v>0.07848046937500262</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.06394276598720991</v>
+        <v>-0.05216273000628309</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.004878723471495576</v>
+        <v>0.06752185265458148</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0.03488915224583591</v>
+        <v>0.001822964442082464</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.03003689220642247</v>
+        <v>0.2557052888742755</v>
       </c>
       <c r="FH3" t="n">
         <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0.06000123487803049</v>
+        <v>-0.0158214162903902</v>
       </c>
       <c r="FJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.09443853360326596</v>
+        <v>0.05252396620508305</v>
       </c>
       <c r="FL3" t="n">
         <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>-0.1436425683059086</v>
+        <v>0.08037561763644213</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.06685177547565639</v>
+        <v>0.2621281106307853</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.06739231381642058</v>
+        <v>-0.1723239808415588</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.08366143330944349</v>
+        <v>0.1034101413290576</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0.1147662513825859</v>
+        <v>0.05355040521429349</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.0080864288198161</v>
+        <v>0.1310150946013236</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.08859242636803462</v>
+        <v>-0.05815442226896428</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0.1157175557866199</v>
+        <v>0.0781747160930705</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -2137,37 +2137,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.08965150017321916</v>
+        <v>0.4844131650060651</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0170789610339525</v>
+        <v>0.05311733254361795</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05352850468919734</v>
+        <v>-0.3492477739920528</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06956041941136624</v>
+        <v>0.4889238887847571</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,70 +2176,70 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01092649068596171</v>
+        <v>-0.09644525125125132</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.04080451336594818</v>
+        <v>-0.2928742680399893</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01004583688780034</v>
+        <v>-0.001482564727059608</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.02228672003403406</v>
+        <v>-0.102538350536024</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.01495497450072333</v>
+        <v>-0.1538574340362115</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02547407592521764</v>
+        <v>0.1501523851957632</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01762808769943115</v>
+        <v>-0.08931700704516032</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.01301757867274005</v>
+        <v>0.09643237566764525</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
@@ -2248,22 +2248,22 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0115651996263843</v>
+        <v>0.2048399742946764</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.006009181088453967</v>
+        <v>0.04036232870255291</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.04227263681546259</v>
+        <v>-0.2145341422518564</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
@@ -2272,55 +2272,55 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0791834664481947</v>
+        <v>0.5966605972794835</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.00123275824311689</v>
+        <v>-0.2643320705026265</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.04672808746059894</v>
+        <v>-0.2919498676352363</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.05291695061004667</v>
+        <v>0.1078024968044161</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.04264598205207718</v>
+        <v>0.04113399145921885</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.03376702912166076</v>
+        <v>-0.2517376793973952</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>-0</v>
@@ -2329,34 +2329,34 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.03706896050709246</v>
+        <v>0.07803386568860132</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.01945993885466902</v>
+        <v>0.1397944654434557</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01572102095923825</v>
+        <v>0.1646579879782323</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.04761814820520714</v>
+        <v>0.3641156825683358</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,13 +2365,13 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.001193858673153701</v>
+        <v>-0.1006613484352082</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.03107683892657171</v>
+        <v>-0.3834940306646148</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>-0</v>
@@ -2380,25 +2380,25 @@
         <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.02672163540345887</v>
+        <v>-0.2993434687534735</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.00254469009921057</v>
+        <v>-0.05360629574573329</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.02544756870592889</v>
+        <v>0.2513151762965181</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
@@ -2410,22 +2410,22 @@
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.006407012543007865</v>
+        <v>-0.1723010100540525</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.000174951477567018</v>
+        <v>0.07148619883260734</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.008042889653908949</v>
+        <v>0.09065245606583819</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
         <v>0</v>
@@ -2434,22 +2434,22 @@
         <v>0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.02331500158105047</v>
+        <v>-0.2802247214400514</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.001623864544739637</v>
+        <v>-0.03319214864478054</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03029166608282225</v>
+        <v>0.2427639381734246</v>
       </c>
       <c r="DB4" t="n">
         <v>-0</v>
@@ -2464,19 +2464,19 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.007282102153568164</v>
+        <v>-0.06164222275749897</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
         <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01517312774977101</v>
+        <v>-0.05681657835884071</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.02439934094661182</v>
+        <v>0.1497792705841469</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,25 +2485,25 @@
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.007926680405662016</v>
+        <v>-0.08925946895763845</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.04092671565278319</v>
+        <v>-0.04073309151278353</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.007614787452195921</v>
+        <v>0.09734883734959447</v>
       </c>
       <c r="DT4" t="n">
         <v>0</v>
@@ -2518,46 +2518,46 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.02406642314660831</v>
+        <v>0.1457076489067203</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
         <v>0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.02425716484874411</v>
+        <v>0.00293357408186951</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.01012486991713645</v>
+        <v>0.03927220844744345</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.01975550624407111</v>
+        <v>-0.1340489075262917</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.005198459933053023</v>
+        <v>-0.1154504523673243</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01114131142010665</v>
+        <v>0.1871838062474707</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
@@ -2566,82 +2566,82 @@
         <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.02555568749511729</v>
+        <v>-0.2200037847771356</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01888572186811287</v>
+        <v>-0.1313507105430612</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.02215223780885942</v>
+        <v>0.1540492485280741</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.02421747896600241</v>
+        <v>-0.2964211232749775</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.005820635238728196</v>
+        <v>-0.09458093912709896</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03008058881379578</v>
+        <v>0.2322318474125914</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01075231406612672</v>
+        <v>-0.1852096003502512</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.0304223936321125</v>
+        <v>0.04058384000910006</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.02267973957311843</v>
+        <v>0.3065707790467048</v>
       </c>
       <c r="FM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN4" t="n">
         <v>0</v>
@@ -2650,10 +2650,10 @@
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.01319409686276548</v>
+        <v>-0.06285084487746141</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
@@ -2662,43 +2662,43 @@
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.002071910606969006</v>
+        <v>0.008371791587602609</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0.0008214566873142054</v>
+        <v>-0.01139848987119247</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02556598483244166</v>
+        <v>-0.1534560777802785</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.01600642956751079</v>
+        <v>0.150081544892725</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
         <v>-0</v>
@@ -2709,46 +2709,46 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.692670946117389</v>
+        <v>0.3029222010441324</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2815834510071579</v>
+        <v>-0.205127275888712</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1527192508473082</v>
+        <v>0.0550872146255813</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5992279006726873</v>
+        <v>0.3389390355339809</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1770090755289702</v>
+        <v>-0.1844324868528202</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1738228767444187</v>
+        <v>0.03138364521682779</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5" t="n">
         <v>-0</v>
@@ -2763,76 +2763,76 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1918799220474211</v>
+        <v>0.05093440021680862</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.011118076433017</v>
+        <v>-0.02503489472825252</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07242842753597387</v>
+        <v>-0.1096818057286069</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2499598131161106</v>
+        <v>0.1243625914986057</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.009112932129526661</v>
+        <v>-0.1039621495805605</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.09876115605476989</v>
+        <v>-0.1323822081352738</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.08298953090992797</v>
+        <v>0.2264933280752169</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.1371368262749483</v>
+        <v>-0.1021101003976475</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.1215438722773358</v>
+        <v>0.07155610209756601</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2841,19 +2841,19 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.6396442157093252</v>
+        <v>0.2994749101602632</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.1203572486727414</v>
+        <v>-0.1093080657718349</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.05423751818533025</v>
+        <v>-0.06491995334144342</v>
       </c>
       <c r="AY5" t="n">
         <v>-0</v>
@@ -2868,19 +2868,19 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1855895593369498</v>
+        <v>-0.01712298617518117</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.0770297466996961</v>
+        <v>-0.0440973588674639</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.2072777891875343</v>
+        <v>-0.06968296199144704</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -2898,16 +2898,16 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.09215623169501821</v>
+        <v>0.01255153853708868</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1390875333286443</v>
+        <v>0.04691531338627493</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1965739366757976</v>
+        <v>0.04771751143876753</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
@@ -2925,25 +2925,25 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.4596203604854779</v>
+        <v>0.2477793996941698</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.05835938774371055</v>
+        <v>-0.126163759909023</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1030839412799431</v>
+        <v>0.01316809191153496</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -2952,52 +2952,52 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1941620129679794</v>
+        <v>-0.1933569343808738</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.06585729093478764</v>
+        <v>0.1871140784744843</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001616161760998283</v>
+        <v>-0.03130610669893883</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.05835812325868805</v>
+        <v>-0.09938187501334203</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.152470069243465</v>
+        <v>0.3362563401966628</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1797910428862951</v>
+        <v>0.03814619967959786</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
@@ -3006,73 +3006,73 @@
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1984802685331126</v>
+        <v>-0.1773124665098497</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.09731399027518618</v>
+        <v>0.1790633126010306</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.01948827856766514</v>
+        <v>-0.02746124558655496</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.04939647784043341</v>
+        <v>0.03398174647296211</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.3129964140847323</v>
+        <v>0.02014113053266577</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01004066239176944</v>
+        <v>-0.0526900906426382</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1627884437344467</v>
+        <v>-0.1365387775794885</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.1263419212664436</v>
+        <v>0.159882731009755</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.1775936500165514</v>
+        <v>-0.03364333486355517</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
@@ -3084,73 +3084,73 @@
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.2200305173967657</v>
+        <v>-0.1364146302760463</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.09520944382248742</v>
+        <v>-0.07361185650503263</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.07586896562147352</v>
+        <v>-0.133889239952799</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1456541101655162</v>
+        <v>-0.05734700524952092</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.1399655070006554</v>
+        <v>0.1449540187113478</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.1992780891195935</v>
+        <v>0.0199880057149247</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1829819900404266</v>
+        <v>-0.1947948516791903</v>
       </c>
       <c r="EQ5" t="n">
         <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.06689202288078334</v>
+        <v>0.09889540472902465</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02154966093786916</v>
+        <v>0.03829481507956714</v>
       </c>
       <c r="ET5" t="n">
         <v>-0</v>
@@ -3162,22 +3162,22 @@
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1902856047528495</v>
+        <v>-0.2000590066014149</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.1070745199716675</v>
+        <v>0.2066862018562733</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.006683105537652478</v>
+        <v>-0.04370988152978129</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
@@ -3186,25 +3186,25 @@
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.1520362003995589</v>
+        <v>-0.07874066598522657</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.09979224262307176</v>
+        <v>0.07486047568736433</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.05866223300379084</v>
+        <v>-0.2767617189633837</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3216,31 +3216,31 @@
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
         <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.05745841453456233</v>
+        <v>-0.00655562288762624</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>-0.05484806171645745</v>
+        <v>-0.03032194630880169</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.1166191586027453</v>
+        <v>0.03283693440869157</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
@@ -3249,33 +3249,33 @@
         <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.09728524480414069</v>
+        <v>-0.09887440103371867</v>
       </c>
       <c r="GA5" t="n">
         <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.05034085561143231</v>
+        <v>0.2339521564370413</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.2051066660998437</v>
+        <v>0.09987875543777885</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -3284,25 +3284,25 @@
         <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1714264935664901</v>
+        <v>-0.2222300830021783</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1343758463962026</v>
+        <v>0.05954045545677621</v>
       </c>
       <c r="F6" t="n">
         <v>-0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.219750856167513</v>
+        <v>0.06616224874898363</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -3311,25 +3311,25 @@
         <v>-0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06413000689288867</v>
+        <v>-0.2751649180750976</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08378673602555699</v>
+        <v>0.007585528320465437</v>
       </c>
       <c r="O6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04633431967056784</v>
+        <v>-0.01187376013326635</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -3338,91 +3338,91 @@
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1301934867182559</v>
+        <v>-0.05099969969699655</v>
       </c>
       <c r="W6" t="n">
-        <v>0.09600428667436352</v>
+        <v>-0.05695944970537984</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.08782334792201589</v>
+        <v>0.03424941934827228</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.06508627512818815</v>
+        <v>0.04854948269406507</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.04559491928332133</v>
+        <v>0.1474049330451348</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.03450327618544947</v>
+        <v>0.03279467538059166</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.02733925163834371</v>
+        <v>-0.1530487892247109</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.06701396635776023</v>
+        <v>0.03105930195599121</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>-0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.1347445312554785</v>
+        <v>-0.06477837497488191</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.06522536570775357</v>
+        <v>-0.2747449921440352</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.2261708907848533</v>
+        <v>-0.06010969901495966</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
@@ -3437,7 +3437,7 @@
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.2576140985759737</v>
+        <v>0.1800144706142501</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
@@ -3446,37 +3446,37 @@
         <v>-0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.01796306130910487</v>
+        <v>0.2023212111923305</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.04595914133122102</v>
+        <v>0.1711244049944427</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.09441449390773836</v>
+        <v>-0.002302916009784424</v>
       </c>
       <c r="BM6" t="n">
         <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.04716032003109173</v>
+        <v>0.02070231960002991</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.2021465124546372</v>
+        <v>-0.1236089998595658</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
@@ -3485,58 +3485,58 @@
         <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.06356470352526175</v>
+        <v>-0.05881836988943883</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW6" t="n">
         <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.01106478125396982</v>
+        <v>-0.2596430457148038</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1481483898781914</v>
+        <v>-0.04834514594564143</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.0415208048198111</v>
+        <v>-0.05523833054221675</v>
       </c>
       <c r="CE6" t="n">
         <v>0</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0200044353232424</v>
+        <v>0.1289282169638186</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.04805502389604575</v>
+        <v>-0.01160851006997405</v>
       </c>
       <c r="CI6" t="n">
         <v>0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3545,61 +3545,61 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.06355906205621439</v>
+        <v>-4.832128262801541e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.1438284424603799</v>
+        <v>0.127793998099322</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1113321738502481</v>
+        <v>-0.01343936496036688</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.017152650641694</v>
+        <v>-0.04616469580418427</v>
       </c>
       <c r="CW6" t="n">
         <v>-0</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.01560003667645765</v>
+        <v>0.1337586350964637</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.03860107448807707</v>
+        <v>0.001086166788963059</v>
       </c>
       <c r="DA6" t="n">
         <v>-0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.02622812487016317</v>
+        <v>-0.01483021363417152</v>
       </c>
       <c r="DF6" t="n">
         <v>-0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1003285448673639</v>
+        <v>0.1242417177640168</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.05346167297353791</v>
+        <v>-0.01855691375465265</v>
       </c>
       <c r="DJ6" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.05556455928673473</v>
+        <v>-0.05932478266720421</v>
       </c>
       <c r="DO6" t="n">
         <v>-0</v>
@@ -3635,70 +3635,70 @@
         <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.07992444007308216</v>
+        <v>-0.002111907790682653</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.1278937418203414</v>
+        <v>0.009992672631214478</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.08621647363586943</v>
+        <v>0.001802470872078716</v>
       </c>
       <c r="DX6" t="n">
         <v>-0</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.03351143051283249</v>
+        <v>0.04620580049393943</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.1177773003941129</v>
+        <v>0.02888325003691535</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.04521071787726483</v>
+        <v>-0.09783759962060092</v>
       </c>
       <c r="EG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.04067760406885485</v>
+        <v>0.1069754599369691</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.02560340079816104</v>
+        <v>0.02997231496116799</v>
       </c>
       <c r="EK6" t="n">
         <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>0</v>
@@ -3707,22 +3707,22 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.01234673250564037</v>
+        <v>0.03249227295703395</v>
       </c>
       <c r="EP6" t="n">
         <v>0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.04859036362260431</v>
+        <v>0.1364325870705268</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01396564145714593</v>
+        <v>0.002298247504308305</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3734,34 +3734,34 @@
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.02327278093876996</v>
+        <v>-0.05127275116494236</v>
       </c>
       <c r="EY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0.006306935649271228</v>
+        <v>0.1641467756134921</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.05011858918225799</v>
+        <v>-0.003001145721867552</v>
       </c>
       <c r="FC6" t="n">
         <v>0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0.05412444194926366</v>
+        <v>0.006739624008693489</v>
       </c>
       <c r="FH6" t="n">
         <v>0</v>
@@ -3770,10 +3770,10 @@
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.04216231585267493</v>
+        <v>0.09887710876572092</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.2391614221495183</v>
+        <v>0.1096442008299125</v>
       </c>
       <c r="FL6" t="n">
         <v>0</v>
@@ -3782,40 +3782,40 @@
         <v>-0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
         <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.01270610679242614</v>
+        <v>-0.01505809145220881</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
       </c>
       <c r="FS6" t="n">
-        <v>-0.04497790953649969</v>
+        <v>0.2434142538652261</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.07970831105080561</v>
+        <v>0.06012350885646863</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW6" t="n">
         <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.04280526321271828</v>
+        <v>0.02131986457976425</v>
       </c>
       <c r="FZ6" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.0564743459876418</v>
+        <v>0.1944733630616521</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4898863792298052</v>
+        <v>0.2940939747123159</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2195734571514498</v>
+        <v>-0.1142418560559098</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004301840717020753</v>
+        <v>-0.002775740693596804</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5012,16 +5012,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3230576441928116</v>
+        <v>0.3208691471560133</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2347931730604849</v>
+        <v>-0.1725661262993227</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01963735807578127</v>
+        <v>-0.06209959793109149</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5039,70 +5039,70 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.116795392838721</v>
+        <v>0.05355400380390189</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.003155487219000597</v>
+        <v>-0.04258901447036365</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1984898868641507</v>
+        <v>-0.07246086673008613</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.08923677184336534</v>
+        <v>-0.05058009290139544</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0334627397672863</v>
+        <v>-0.1098834173783863</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.08288082873448363</v>
+        <v>-0.0001717206941538779</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.007406334071115631</v>
+        <v>0.07758667358099709</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.07689087401552307</v>
+        <v>-0.08883542302473293</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.001953082809698603</v>
+        <v>0.09189087085963844</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5120,52 +5120,52 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.38170823464185</v>
+        <v>0.2007514856239647</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.03360338317178071</v>
+        <v>-0.02360624768411911</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1485579590111811</v>
+        <v>-0.08290826182834257</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.06668318671420971</v>
+        <v>-0.008617249076486224</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.2287165602604183</v>
+        <v>-0.02409514979637597</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1509255100318254</v>
+        <v>-0.04971202545165655</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,100 +5174,100 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1228957761028466</v>
+        <v>-0.02785743207074556</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.03456364667549564</v>
+        <v>0.03194768022615089</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.2249607232691341</v>
+        <v>0.07562537946464498</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1870974677408242</v>
+        <v>0.1463730062421196</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0363810775801828</v>
+        <v>-0.08591627634841652</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.1309739535366376</v>
+        <v>-0.01646122356952214</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1250204366068784</v>
+        <v>-0.1185473580204218</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002289993948184891</v>
+        <v>0.08386240635992476</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.02574816397850176</v>
+        <v>-0.0002282727446811588</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.005093997553190948</v>
+        <v>-0.05017137549725521</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.2221832755519027</v>
+        <v>0.1548709388392656</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1004411567920544</v>
+        <v>0.03533373588298382</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5279,19 +5279,19 @@
         <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.08905663842743793</v>
+        <v>-0.1184437034104061</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0496666153297285</v>
+        <v>0.08954339631191113</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.04054527860986346</v>
+        <v>0.008879315492764966</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5309,16 +5309,16 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.005592214626901436</v>
+        <v>-0.04957948330297226</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.106874327834612</v>
+        <v>0.009562762948189699</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.008532273804238792</v>
+        <v>-0.1210673657030086</v>
       </c>
       <c r="DJ9" t="n">
         <v>-0</v>
@@ -5330,31 +5330,31 @@
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.08309583375135474</v>
+        <v>-0.04908179148022496</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.008468719726991095</v>
+        <v>-0.07862817596791746</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.06070507028772641</v>
+        <v>-0.07466599185890922</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
@@ -5363,43 +5363,43 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.0558436782948882</v>
+        <v>-0.03051357856030717</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.0387503176897569</v>
+        <v>0.04914536659323656</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.06375108170628249</v>
+        <v>-0.001175911876166117</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.1018504226936212</v>
+        <v>-0.09835577594358555</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0.005733721615622637</v>
+        <v>0.04393093474765612</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.08744685921344626</v>
+        <v>0.06479681605823728</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
@@ -5414,22 +5414,22 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.01885828405238825</v>
+        <v>-0.01732176588501542</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.01717474344817701</v>
+        <v>0.004605099037338692</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.008580747420324886</v>
+        <v>-0.006439077250370216</v>
       </c>
       <c r="ET9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU9" t="n">
         <v>0</v>
@@ -5438,49 +5438,49 @@
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.0866902732988466</v>
+        <v>-0.1236725071213241</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0.01181380698303513</v>
+        <v>0.113164796830074</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.006135971483560244</v>
+        <v>-0.01422254760136715</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.01021811244340338</v>
+        <v>0.1289737980647091</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0004571318691481522</v>
+        <v>0.09297641644652327</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.01892520848862679</v>
+        <v>0.01137628000730872</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5492,22 +5492,22 @@
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.03772142495823642</v>
+        <v>0.05612390481615505</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0269585602647292</v>
+        <v>0.1338461531522418</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.05362702661600456</v>
+        <v>-0.03775076182792581</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
@@ -5522,19 +5522,19 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.07478927210817721</v>
+        <v>-0.07691923220130799</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.1263203274476374</v>
+        <v>0.03253176874929289</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
         <v>-0</v>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.152873668995078</v>
+        <v>0.1956997412481772</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,25 +5563,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.04585241272696219</v>
+        <v>0.01088603747028149</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0794794516633283</v>
+        <v>-0.08012748889050444</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1261164459681745</v>
+        <v>0.2209982326011991</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,13 +5590,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.03476140764808417</v>
+        <v>-0.03585158223242486</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.07492785439977322</v>
+        <v>-0.09657535491594579</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -5605,49 +5605,49 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01163091317889218</v>
+        <v>0.0583116014525905</v>
       </c>
       <c r="U10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0007426299360666515</v>
+        <v>-0.06235464903714049</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01532728809926734</v>
+        <v>-0.002427193126092907</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.005969581944613358</v>
+        <v>-0.03067145781424573</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01875294401366824</v>
+        <v>-0.1272020798736707</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.005562864680223214</v>
+        <v>0.01872435445431386</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -5662,22 +5662,22 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01024618941514646</v>
+        <v>0.0242758660882817</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01582463757297696</v>
+        <v>-0.02061026853056282</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.01357930372702509</v>
+        <v>-0.001350766297879431</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,10 +5686,10 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1003293620136138</v>
+        <v>0.1344902232313336</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,25 +5698,25 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.007259138254044659</v>
+        <v>-0.08948416123894261</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.007753969342811263</v>
+        <v>-0.03716578395458003</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
         <v>-0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.04204083395759653</v>
+        <v>0.01111499780413116</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,52 +5725,52 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.06279641786391224</v>
+        <v>-0.01195897750479191</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.08430639893907166</v>
+        <v>-0.05644867337816323</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.04432716305521988</v>
+        <v>0.00749465859015886</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02439380207452361</v>
+        <v>0.06283859497277466</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.02146400247610832</v>
+        <v>-0.00325298405366368</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.05404348012978649</v>
+        <v>0.09678243954028662</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,10 +5779,10 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.004910684894858203</v>
+        <v>-0.01383165583226981</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.003460111703349216</v>
+        <v>-0.05878830445210886</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5791,28 +5791,28 @@
         <v>-0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.0287376372542208</v>
+        <v>-0.06098000035532846</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0001614260587979783</v>
+        <v>0.003042809791651795</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02486390245792601</v>
+        <v>0.03516190798625649</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>-0</v>
@@ -5824,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.004840915072713716</v>
+        <v>-0.01721639202871783</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
@@ -5833,64 +5833,64 @@
         <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.002612768088029897</v>
+        <v>0.06314483066604984</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.02122000617110018</v>
+        <v>0.05444822111701842</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02355057423762089</v>
+        <v>-0.06251444266086598</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.003684508522459971</v>
+        <v>0.0007918701639229419</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.02508456539308271</v>
+        <v>0.04960899351521418</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.01471175745172174</v>
+        <v>-0.01889625603171146</v>
       </c>
       <c r="DG10" t="n">
         <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0260531556355841</v>
+        <v>-0.08326702291000873</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.001191939362927994</v>
+        <v>0.04567435442026722</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
@@ -5905,46 +5905,46 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.009457229597875559</v>
+        <v>-0.0145363097059214</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01365078430856105</v>
+        <v>-0.05591899785563391</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.01275840276073518</v>
+        <v>0.02578345421164845</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.04141920125464937</v>
+        <v>0.01149152689219493</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.01758971972289809</v>
+        <v>-0.05038403721543512</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.008155823214846316</v>
+        <v>0.01430939768732798</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
@@ -5953,13 +5953,13 @@
         <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.03354977044762174</v>
+        <v>-0.03628622964739785</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
@@ -5968,13 +5968,13 @@
         <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.007641230795468463</v>
+        <v>0.01841548028115032</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.02430209170483043</v>
+        <v>-0.0009829606754570761</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,22 +5983,22 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.01505852129638553</v>
+        <v>-0.0105138077209176</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.003490233596562857</v>
+        <v>0.0001585939771776998</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.009187385830616113</v>
+        <v>0.06694574353344411</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
@@ -6007,58 +6007,58 @@
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.02392794350498679</v>
+        <v>-0.06934142242398773</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.007301785558178113</v>
+        <v>-0.01285523657458626</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.02905866878865762</v>
+        <v>0.03001982945830428</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>-0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.02717315641628882</v>
+        <v>0.1164506683103962</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.00865225756563045</v>
+        <v>-0.05049560506040895</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.01337092357926712</v>
+        <v>0.07840587794700224</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
@@ -6067,37 +6067,37 @@
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.009515734159440434</v>
+        <v>0.03337397520192521</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.01625152732836119</v>
+        <v>-0.0550621297200769</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.008605018943952681</v>
+        <v>-0.02406715755016766</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.006621830061819618</v>
+        <v>-0.03241427456517686</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
@@ -6106,16 +6106,16 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.009277019959012983</v>
+        <v>0.05372688422352246</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5583645709570435</v>
+        <v>0.260989281655959</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1918499696725843</v>
+        <v>-0.1359947066724072</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.08014143578261618</v>
+        <v>-0.0330767219276205</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -6150,16 +6150,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.375452992702587</v>
+        <v>0.2866794046771792</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1874508233636335</v>
+        <v>-0.1753110302487711</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0676847509067984</v>
+        <v>-0.06199007464104946</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -6177,79 +6177,79 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1213318878461047</v>
+        <v>0.05085113083324453</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0228317393835805</v>
+        <v>-0.0461337483615858</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1143085542444814</v>
+        <v>-0.06113114451893</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02102114163106059</v>
+        <v>-0.06881040095147828</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.004206518486527301</v>
+        <v>-0.09139801306158089</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.03177331712610375</v>
+        <v>-0.03971884419337465</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03024105259020758</v>
+        <v>0.07983159127082506</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.07060731372709193</v>
+        <v>-0.08934625632318106</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.04058631738227208</v>
+        <v>0.04426863834056241</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -6258,52 +6258,52 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.3916144720079905</v>
+        <v>0.1815187630856613</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0158493562844335</v>
+        <v>-0.04216209277237171</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.06823745826401356</v>
+        <v>-0.07548373668764541</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.04179220658350058</v>
+        <v>-0.02032995211958848</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.1966582865466927</v>
+        <v>-0.03110157624403819</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1298599174131333</v>
+        <v>-0.02501115157525793</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,19 +6312,19 @@
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1504419085170852</v>
+        <v>-0.004976618208525567</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.08377009372295414</v>
+        <v>0.04873863158507162</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1786123441145687</v>
+        <v>0.05389711526830079</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
         <v>0</v>
@@ -6333,52 +6333,52 @@
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2165233493030241</v>
+        <v>0.160119253350596</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.01167025754586231</v>
+        <v>-0.106639717125916</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0422559233952523</v>
+        <v>-0.01079872638453564</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1208158289882797</v>
+        <v>-0.08551184054631329</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0.0002781696914106662</v>
+        <v>0.08496589405837891</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.02009324824438892</v>
+        <v>-0.0002201142932838355</v>
       </c>
       <c r="CI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
@@ -6390,19 +6390,19 @@
         <v>0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.01874330016033296</v>
+        <v>-0.06406123948364378</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.1261508543876563</v>
+        <v>0.1218827774649552</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1172792836709362</v>
+        <v>0.00698966778217554</v>
       </c>
       <c r="CR11" t="n">
         <v>-0</v>
@@ -6411,7 +6411,7 @@
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
         <v>-0</v>
@@ -6420,22 +6420,22 @@
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.07962232009027953</v>
+        <v>-0.08398360527050917</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0523748631882841</v>
+        <v>0.08789306063736746</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.03207117958295563</v>
+        <v>0.01072223468602499</v>
       </c>
       <c r="DA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6447,16 +6447,16 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.02094669734265907</v>
+        <v>-0.07068555348717821</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.09921457320081781</v>
+        <v>0.02124121595543873</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.03049598773728608</v>
+        <v>-0.02797901974758015</v>
       </c>
       <c r="DJ11" t="n">
         <v>-0</v>
@@ -6471,28 +6471,28 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.1196678797241494</v>
+        <v>-0.04763608982622791</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.01077100926785784</v>
+        <v>-0.01788229456259954</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.06116812430829569</v>
+        <v>-0.02838700257331447</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,16 +6501,16 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.1027227734412667</v>
+        <v>0.01037892770820112</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.005684096072727032</v>
+        <v>0.07029098084438667</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.05545843484507467</v>
+        <v>-0.03320976802367565</v>
       </c>
       <c r="EB11" t="n">
         <v>-0</v>
@@ -6522,49 +6522,49 @@
         <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.09728665395825579</v>
+        <v>-0.06607708163683104</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.006702778819567382</v>
+        <v>0.05936402772657783</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.06916407189913926</v>
+        <v>0.05465512967198341</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
         <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0485521486580312</v>
+        <v>-0.03352265693731168</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0.02513369913965888</v>
+        <v>0.05471009843638479</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01482365450398025</v>
+        <v>-0.01274424599287957</v>
       </c>
       <c r="ET11" t="n">
         <v>0</v>
@@ -6582,43 +6582,43 @@
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.077015597587516</v>
+        <v>-0.09257205197840249</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>9.279459167337774e-06</v>
+        <v>0.1062248301890363</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.007881825411555972</v>
+        <v>-0.006235718391449872</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.0537867039956603</v>
+        <v>0.1016530772554277</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>-0.001689277994626403</v>
+        <v>0.06391250907871519</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.04957122602049302</v>
+        <v>-0.01372187798309528</v>
       </c>
       <c r="FL11" t="n">
         <v>-0</v>
@@ -6630,28 +6630,28 @@
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.05654799493889806</v>
+        <v>0.04099973610072592</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.03109406867981772</v>
+        <v>0.1067056076924024</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.08631498349291195</v>
+        <v>-0.03519835895865128</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>-0</v>
@@ -6660,39 +6660,39 @@
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.08966215093649392</v>
+        <v>-0.0592349595106546</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.1206755482296494</v>
+        <v>0.0286774902767129</v>
       </c>
       <c r="GC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.7520904577435688</v>
+        <v>-0.2926437211797694</v>
       </c>
       <c r="C12" t="n">
         <v>-0</v>
@@ -6701,13 +6701,13 @@
         <v>-0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2140990174216457</v>
+        <v>0.05361464075147683</v>
       </c>
       <c r="F12" t="n">
-        <v>1.225591647447795</v>
+        <v>0.5367326828817879</v>
       </c>
       <c r="G12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -6716,10 +6716,10 @@
         <v>-0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6791643350584414</v>
+        <v>-0.4668156991607339</v>
       </c>
       <c r="L12" t="n">
         <v>-0</v>
@@ -6728,52 +6728,52 @@
         <v>-0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.04376961021011115</v>
+        <v>0.0851003771274239</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9157833256795846</v>
+        <v>0.638150090090958</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.03513257293227368</v>
+        <v>-0.1185175150799476</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
         <v>-0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2743342085485395</v>
+        <v>0.09755380956073698</v>
       </c>
       <c r="X12" t="n">
-        <v>0.05199784595634793</v>
+        <v>0.091699451926197</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03190013380969849</v>
+        <v>0.0586842040599618</v>
       </c>
       <c r="AD12" t="n">
         <v>-0</v>
@@ -6782,16 +6782,16 @@
         <v>-0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1301803602316647</v>
+        <v>0.1925053913156595</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.1383670084954971</v>
+        <v>-0.0622805935436717</v>
       </c>
       <c r="AH12" t="n">
         <v>-0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>-0</v>
@@ -6800,7 +6800,7 @@
         <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.05377330065759508</v>
+        <v>-0.0648952242863777</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
@@ -6809,13 +6809,13 @@
         <v>-0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.07080179392821848</v>
+        <v>0.007969949891716135</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.2033781667324231</v>
+        <v>0.09094435844003546</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -6824,37 +6824,37 @@
         <v>-0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.371239415460371</v>
+        <v>-0.4320583996691659</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.320333892501329</v>
+        <v>0.05653267964450447</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.641899435258263</v>
+        <v>0.2607911871441217</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.2316922894782836</v>
+        <v>0.1856862709313391</v>
       </c>
       <c r="BE12" t="n">
         <v>-0</v>
@@ -6863,10 +6863,10 @@
         <v>-0</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.1387950174244062</v>
+        <v>0.1170275216246781</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.3142908783603678</v>
+        <v>0.05446591695577804</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
@@ -6875,52 +6875,52 @@
         <v>0</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>-0.3028099754903851</v>
+        <v>-0.1439121694416008</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.1374008754791492</v>
+        <v>-0.1084555026203271</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.05566555491796815</v>
+        <v>-0.1360034615037538</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>-0.3906016491980137</v>
+        <v>-0.3172998315423484</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>-0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.1539761856008949</v>
+        <v>-0.0259527010782027</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.3740954655594676</v>
+        <v>0.2363543268257</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
@@ -6932,25 +6932,25 @@
         <v>-0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.1360037703279407</v>
+        <v>0.09902812757506467</v>
       </c>
       <c r="CF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG12" t="n">
         <v>0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.03700158132728459</v>
+        <v>-0.04686459843384086</v>
       </c>
       <c r="CI12" t="n">
-        <v>-0.2498778118308305</v>
+        <v>-0.1431044551434264</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6962,7 +6962,7 @@
         <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.003697159405518862</v>
+        <v>0.131949878590216</v>
       </c>
       <c r="CO12" t="n">
         <v>0</v>
@@ -6971,16 +6971,16 @@
         <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.2821167702866605</v>
+        <v>-0.05424551194965047</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.05008163252390485</v>
+        <v>0.0167470863443324</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU12" t="n">
         <v>0</v>
@@ -6989,22 +6989,22 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.1196367418857527</v>
+        <v>0.09434659037088505</v>
       </c>
       <c r="CX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY12" t="n">
         <v>-0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.06691504289975812</v>
+        <v>-0.04822944886888668</v>
       </c>
       <c r="DA12" t="n">
-        <v>-0.2639212790441514</v>
+        <v>-0.1709032477658985</v>
       </c>
       <c r="DB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7013,22 +7013,22 @@
         <v>-0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.2309986497022291</v>
+        <v>0.1372814434687969</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.3107523399320556</v>
+        <v>0.09219227936881529</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.03726631838653221</v>
+        <v>-0.01326875627739377</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7037,25 +7037,25 @@
         <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.01858886843753602</v>
+        <v>-0.03235745870430893</v>
       </c>
       <c r="DP12" t="n">
         <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.08327988243733561</v>
+        <v>0.05527745274793971</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0.1336207069175909</v>
+        <v>-0.1744855846405945</v>
       </c>
       <c r="DT12" t="n">
         <v>0</v>
@@ -7067,10 +7067,10 @@
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.08660517491064833</v>
+        <v>0.1362773676223452</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
@@ -7079,10 +7079,10 @@
         <v>0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.09538108247331702</v>
+        <v>-0.005237709136767526</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0.1339785633174689</v>
+        <v>0.001419883878133368</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
@@ -7091,31 +7091,31 @@
         <v>-0</v>
       </c>
       <c r="EE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF12" t="n">
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.1010632422762717</v>
+        <v>0.0601653448786814</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>-0.06337816534962909</v>
+        <v>-0.02453797005103952</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0.2141316807994654</v>
+        <v>-0.03895313429141133</v>
       </c>
       <c r="EL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>0</v>
@@ -7124,34 +7124,34 @@
         <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.06915331574419964</v>
+        <v>0.0566095008242851</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.02026919290220554</v>
+        <v>-0.04740390774833865</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0.006628849796097354</v>
+        <v>0.09412866018650821</v>
       </c>
       <c r="EU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV12" t="n">
         <v>-0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.1037596558866079</v>
+        <v>0.1129181185731534</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
@@ -7160,13 +7160,13 @@
         <v>0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.06812609777656969</v>
+        <v>-0.006971492361846916</v>
       </c>
       <c r="FC12" t="n">
-        <v>-0.2327758939433711</v>
+        <v>-0.1443765206893902</v>
       </c>
       <c r="FD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7178,7 +7178,7 @@
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.05351513659863656</v>
+        <v>-0.05764129200599305</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,10 +7187,10 @@
         <v>0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.003781138971022557</v>
+        <v>0.01697837921711391</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0.1766410619563688</v>
+        <v>-0.126829286688698</v>
       </c>
       <c r="FM12" t="n">
         <v>-0</v>
@@ -7199,13 +7199,13 @@
         <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.03314459563035038</v>
+        <v>0.01819791900562197</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
@@ -7214,37 +7214,37 @@
         <v>0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.1310521430754595</v>
+        <v>0.1451078360269831</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0.1313190489258594</v>
+        <v>0.156489014725728</v>
       </c>
       <c r="FV12" t="n">
         <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.03102262984926365</v>
+        <v>0.06896045110250063</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
         <v>0</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.000900414725728538</v>
+        <v>-0.1187721735075542</v>
       </c>
       <c r="GE12" t="n">
         <v>0</v>
@@ -7258,25 +7258,25 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.6263832898005766</v>
+        <v>-0.2911109635260134</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2649003859054163</v>
+        <v>0.1913439824444538</v>
       </c>
       <c r="F13" t="n">
-        <v>0.94976152783862</v>
+        <v>0.272935118598266</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -7285,25 +7285,25 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4663696943184349</v>
+        <v>-0.2565672935172608</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2540614654827956</v>
+        <v>0.2649964225666426</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8144316868934315</v>
+        <v>0.4472238719176917</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -7312,64 +7312,64 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.08732890430446363</v>
+        <v>-0.006154966326530762</v>
       </c>
       <c r="T13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>-0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2423384428608235</v>
+        <v>0.02589364239963958</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1724106598981262</v>
+        <v>0.07241151162526378</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.0650829520428097</v>
+        <v>0.04586666031937985</v>
       </c>
       <c r="AC13" t="n">
         <v>-0</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>-0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.08700283111161761</v>
+        <v>0.02682084855201298</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.06740393108866746</v>
+        <v>-0.06269273265925215</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.1476898807076158</v>
+        <v>-0.04809139724388358</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,64 +7378,64 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.09027526504992242</v>
+        <v>-0.09087670402858372</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.1348720221757201</v>
+        <v>0.02858408712757603</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0.4448109064662223</v>
+        <v>-0.2157404933421607</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW13" t="n">
         <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.2156906137463059</v>
+        <v>-0.06932014696249814</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.3995837833500135</v>
+        <v>0.2968031628414719</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0.1009811405320288</v>
+        <v>0.001886462314449668</v>
       </c>
       <c r="BD13" t="n">
         <v>-0</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
         <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.07844045528853054</v>
+        <v>0.1127771531983743</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.2675494808129998</v>
+        <v>-0.08215545534155447</v>
       </c>
       <c r="BI13" t="n">
         <v>-0</v>
@@ -7447,7 +7447,7 @@
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0.00837440999730292</v>
+        <v>0.07774749295891641</v>
       </c>
       <c r="BM13" t="n">
         <v>0</v>
@@ -7459,118 +7459,118 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.03262800729064194</v>
+        <v>0.04030790826902256</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0.002595374667331275</v>
+        <v>-0.02403328150665655</v>
       </c>
       <c r="BR13" t="n">
         <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
         <v>-0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0.2273299029261642</v>
+        <v>-0.1072564097898781</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1743161567832233</v>
+        <v>0.1178298721200098</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.3492650432421383</v>
+        <v>0.2142966012708697</v>
       </c>
       <c r="CA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.1466973193875671</v>
+        <v>0.09499499174263917</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.1083026618481219</v>
+        <v>-0.0500973580442227</v>
       </c>
       <c r="CI13" t="n">
-        <v>-0.1886186134081402</v>
+        <v>-0.08860723243111654</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-0.01875334290578856</v>
+        <v>-0.004956680000799645</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
         <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.2252678630338915</v>
+        <v>-0.06866485589434905</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.0512286086547812</v>
+        <v>-0.09484076905556717</v>
       </c>
       <c r="CS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.1423909425215244</v>
+        <v>0.1091769567567201</v>
       </c>
       <c r="CW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.1195278599833101</v>
+        <v>-0.09128039870070059</v>
       </c>
       <c r="DA13" t="n">
-        <v>-0.2003687367996605</v>
+        <v>-0.0976278533741485</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7579,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0002101936709146741</v>
+        <v>0.0046149535977101</v>
       </c>
       <c r="DF13" t="n">
         <v>-0</v>
@@ -7591,25 +7591,25 @@
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.02702742021236096</v>
+        <v>-0.02466953918568698</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.02854417735916088</v>
+        <v>-0.03477434490565828</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.02557867975659735</v>
+        <v>0.01110159633016498</v>
       </c>
       <c r="DO13" t="n">
         <v>0</v>
@@ -7621,10 +7621,10 @@
         <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.09624792146319265</v>
+        <v>-0.07893774601432846</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.1366563400087682</v>
+        <v>-0.1093325661647794</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
@@ -7636,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.05797030380971467</v>
+        <v>0.02640869593195508</v>
       </c>
       <c r="DX13" t="n">
         <v>-0</v>
@@ -7648,49 +7648,49 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.06254157145011957</v>
+        <v>-0.1236649074888483</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.1433673708501836</v>
+        <v>-0.07946107166841475</v>
       </c>
       <c r="EC13" t="n">
         <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.1169358342177791</v>
+        <v>0.0369474539328886</v>
       </c>
       <c r="EG13" t="n">
         <v>-0</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.1277663371391074</v>
+        <v>-0.04870299051753234</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0.2001490593580545</v>
+        <v>-0.04029733042393016</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0.09312358941283772</v>
+        <v>-0.04757453606569571</v>
       </c>
       <c r="EP13" t="n">
         <v>-0</v>
@@ -7702,10 +7702,10 @@
         <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.109772686334006</v>
+        <v>0.006257108692813211</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0.0392422289952717</v>
+        <v>-0.06749811371138631</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
@@ -7714,13 +7714,13 @@
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.1251982994794262</v>
+        <v>0.1025797308354388</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,10 +7729,10 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.1273008022724653</v>
+        <v>-0.06586379756635566</v>
       </c>
       <c r="FC13" t="n">
-        <v>-0.1907074661327267</v>
+        <v>-0.09777211682122439</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
@@ -7741,37 +7741,37 @@
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.06192568629842234</v>
+        <v>0.1367529798997405</v>
       </c>
       <c r="FH13" t="n">
         <v>0</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.08023378657634928</v>
+        <v>0.03533886166502525</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.03082053143386415</v>
+        <v>-0.03407039079778087</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.1236631395122386</v>
+        <v>0.1457258440022274</v>
       </c>
       <c r="FQ13" t="n">
         <v>0</v>
@@ -7780,16 +7780,16 @@
         <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.03567853050519221</v>
+        <v>0.03098421017576839</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.05632624284771327</v>
+        <v>-0.2084201510218378</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW13" t="n">
         <v>0</v>
@@ -7798,13 +7798,13 @@
         <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0.04118008282858749</v>
+        <v>0.02289401763806941</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
         <v>0</v>
@@ -7813,16 +7813,16 @@
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.08204146221067565</v>
+        <v>0.03766764680356449</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,25 +7830,25 @@
         <v>-0</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.3569671946857874</v>
+        <v>-0.2325786990397319</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06656940123547546</v>
+        <v>-0.01623109434973239</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9216725216224668</v>
+        <v>0.440051828394903</v>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
         <v>-0</v>
@@ -7857,7 +7857,7 @@
         <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2737033222309432</v>
+        <v>-0.2321468570486197</v>
       </c>
       <c r="L14" t="n">
         <v>-0</v>
@@ -7866,25 +7866,25 @@
         <v>-0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01658600799988601</v>
+        <v>0.2072158341830356</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7649667451879233</v>
+        <v>0.490964836095762</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.05719204572681222</v>
+        <v>-0.05228533185659725</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
@@ -7893,10 +7893,10 @@
         <v>-0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1686889357409242</v>
+        <v>0.08471441004687189</v>
       </c>
       <c r="X14" t="n">
-        <v>0.06897399773167588</v>
+        <v>0.1416301927572728</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -7908,22 +7908,22 @@
         <v>-0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.05614567959215743</v>
+        <v>0.1466220068396758</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.01007345927082084</v>
+        <v>0.1881765681607018</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.03208653042323651</v>
+        <v>0.1479515111334489</v>
       </c>
       <c r="AH14" t="n">
         <v>-0</v>
@@ -7932,13 +7932,13 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK14" t="n">
         <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.02037371071768949</v>
+        <v>-0.06695490505644855</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
@@ -7947,10 +7947,10 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.03314151075055025</v>
+        <v>-0.1229731536876098</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.1759399421345491</v>
+        <v>0.1043931037609274</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -7965,22 +7965,22 @@
         <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.20859707926766</v>
+        <v>-0.2069201350892532</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1258545862904143</v>
+        <v>0.08607158632076661</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.5977179801262149</v>
+        <v>0.2903261843287781</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
         <v>0</v>
@@ -7989,10 +7989,10 @@
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.1306871269030099</v>
+        <v>0.0529618463056629</v>
       </c>
       <c r="BE14" t="n">
         <v>-0</v>
@@ -8001,37 +8001,37 @@
         <v>-0</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.09974013710805751</v>
+        <v>0.06512581156102711</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.1421953923210451</v>
+        <v>0.1146778027843362</v>
       </c>
       <c r="BI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.1819513713098827</v>
+        <v>0.05646796212578345</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.0449565825088249</v>
+        <v>-0.04984154771542516</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0.01534099958181424</v>
+        <v>0.01659851302570494</v>
       </c>
       <c r="BR14" t="n">
         <v>0</v>
@@ -8046,79 +8046,79 @@
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.1942950071460315</v>
+        <v>-0.2156399270596953</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.1198023333612921</v>
+        <v>0.03991019549209552</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.2972326714326751</v>
+        <v>0.2639013249471278</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD14" t="n">
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.1218587601129074</v>
+        <v>0.1177101719172988</v>
       </c>
       <c r="CF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG14" t="n">
         <v>0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.02780332566428922</v>
+        <v>-0.01812575251768358</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0.1569921936519707</v>
+        <v>-0.1580381203242079</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
         <v>-0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.02884541107586273</v>
+        <v>0.03214182908696249</v>
       </c>
       <c r="CO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP14" t="n">
         <v>0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.1770790714722587</v>
+        <v>-0.1848085939699531</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.04202087806774704</v>
+        <v>-0.2814224874212706</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
@@ -8127,52 +8127,52 @@
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.09653315414127776</v>
+        <v>0.1304755749986602</v>
       </c>
       <c r="CX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY14" t="n">
         <v>-0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.004001961650504946</v>
+        <v>-0.04736665532742319</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0.1669314284311001</v>
+        <v>-0.1753137669230691</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.1164383788079185</v>
+        <v>0.07857739350814202</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.2371704280475662</v>
+        <v>0.2537493281847155</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.02673434692621181</v>
+        <v>-0.0923100205773338</v>
       </c>
       <c r="DK14" t="n">
         <v>-0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
         <v>-0</v>
@@ -8181,19 +8181,19 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.002235822006535227</v>
+        <v>-0.08138346253306197</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ14" t="n">
         <v>-0</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.1461313039804342</v>
+        <v>0.07568398981930524</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.01223239577011441</v>
+        <v>-0.05356619449286939</v>
       </c>
       <c r="DT14" t="n">
         <v>0</v>
@@ -8202,13 +8202,13 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.1030083624061013</v>
+        <v>0.06948231288215648</v>
       </c>
       <c r="DY14" t="n">
         <v>0</v>
@@ -8217,64 +8217,64 @@
         <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.02619482282929341</v>
+        <v>0.1678897146022345</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.1240610339648263</v>
+        <v>-0.1274167933454706</v>
       </c>
       <c r="EC14" t="n">
         <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF14" t="n">
         <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.08718388723853845</v>
+        <v>0.09224925205636794</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.03298838968276102</v>
+        <v>-0.08516093785862645</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0.1460912345016882</v>
+        <v>0.03275069768634659</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.02140715824691693</v>
+        <v>0.06839603842811789</v>
       </c>
       <c r="EQ14" t="n">
         <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.0005751387770164082</v>
+        <v>-0.1181368824711253</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0.0275331746029008</v>
+        <v>-0.2128445917525304</v>
       </c>
       <c r="EU14" t="n">
         <v>-0</v>
@@ -8283,13 +8283,13 @@
         <v>-0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
         <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0757683595024652</v>
+        <v>0.1389361027227752</v>
       </c>
       <c r="EZ14" t="n">
         <v>0</v>
@@ -8298,25 +8298,25 @@
         <v>0</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.02713846110652639</v>
+        <v>0.0008550519441758181</v>
       </c>
       <c r="FC14" t="n">
-        <v>-0.1590163242154568</v>
+        <v>-0.1471495684543165</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.06090043730127295</v>
+        <v>-0.2546625447229255</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
@@ -8325,64 +8325,64 @@
         <v>0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.00184131705350354</v>
+        <v>-0.03299294446017864</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0.08133602047876268</v>
+        <v>-0.18854286665428</v>
       </c>
       <c r="FM14" t="n">
         <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.04521181014366062</v>
+        <v>0.2003929351809805</v>
       </c>
       <c r="FR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS14" t="n">
         <v>0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.2199894422274603</v>
+        <v>-0.07119732382275322</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0.1815904824812834</v>
+        <v>-0.07537536769485459</v>
       </c>
       <c r="FV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX14" t="n">
         <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.0424635482328206</v>
+        <v>0.1088027392748028</v>
       </c>
       <c r="GA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB14" t="n">
         <v>0</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.09134330673832675</v>
+        <v>-0.09668475856608771</v>
       </c>
       <c r="GE14" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.05732411505266691</v>
+        <v>0.008811796326155228</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5587666042653078</v>
+        <v>0.02835316953685584</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
@@ -8408,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3112853669055824</v>
+        <v>-0.07538899747375084</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
@@ -8423,10 +8423,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0311955465058644</v>
+        <v>0.02720748743662773</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3576512310259512</v>
+        <v>0.01371364420311008</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3290948631682928</v>
+        <v>-0.09650503006754327</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -8444,43 +8444,43 @@
         <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.05459591661367025</v>
+        <v>0.03072462606396179</v>
       </c>
       <c r="T15" t="n">
-        <v>0.09943637278768151</v>
+        <v>0.03260312738291845</v>
       </c>
       <c r="U15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0381534313993283</v>
+        <v>-0.002043570632159596</v>
       </c>
       <c r="X15" t="n">
         <v>-0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.04782701465929878</v>
+        <v>-0.01810335944778917</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.2168302266515969</v>
+        <v>0.01127836204420244</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
@@ -8489,64 +8489,64 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.04870322846599174</v>
+        <v>-0.06327578063544077</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.03947883267787088</v>
+        <v>0.009379599078835088</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.04748704916369009</v>
+        <v>0.03001181237810524</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.04380458989417103</v>
+        <v>-0.01162109729330903</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0.007942386031486837</v>
+        <v>0.01361568172826842</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.4647969014891534</v>
+        <v>0.06561712453510361</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.08232723320466985</v>
+        <v>-0.06398389318713633</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
         <v>-0</v>
@@ -8555,28 +8555,28 @@
         <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.01782337058591764</v>
+        <v>-0.008120998840932979</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.08560304295674478</v>
+        <v>-0.01106658984366727</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.2696172007958307</v>
+        <v>-0.006622606070323027</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
         <v>0</v>
@@ -8585,49 +8585,49 @@
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.05813868048347309</v>
+        <v>0.02194911276797328</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.2364757294151906</v>
+        <v>0.03514222602600531</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
         <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1440826042483352</v>
+        <v>0.0230942229656519</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.02695142411300262</v>
+        <v>0.03495553272204141</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2741289847155163</v>
+        <v>0.07014962787162898</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.01233262798707283</v>
+        <v>-0.03678973003307152</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
@@ -8636,13 +8636,13 @@
         <v>-0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.02093874973854538</v>
+        <v>-0.003854939628585027</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.07489175295366908</v>
+        <v>0.004871305445548733</v>
       </c>
       <c r="CF15" t="n">
         <v>-0</v>
@@ -8651,37 +8651,37 @@
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.04802460596123808</v>
+        <v>0.02017678006883973</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>-0</v>
       </c>
       <c r="CM15" t="n">
-        <v>-0.08113030290403724</v>
+        <v>-0.03334510871740194</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.05130960331705298</v>
+        <v>-0.0371590722337823</v>
       </c>
       <c r="CO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1557460046302008</v>
+        <v>0.02044886731051351</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
@@ -8690,22 +8690,22 @@
         <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.009885050603866524</v>
+        <v>-0.006957869119001495</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.04058789083020406</v>
+        <v>0.005568726019154457</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0343371583514962</v>
+        <v>0.01724907981503569</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8714,28 +8714,28 @@
         <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>-0.04124208046554814</v>
+        <v>-0.02421804265026542</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.1015724813196529</v>
+        <v>-0.02692556463300561</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
         <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1403525221635555</v>
+        <v>-0.005729535779783569</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8747,52 +8747,52 @@
         <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0.05182586204693099</v>
+        <v>-0.02419585526642355</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.02621277342157687</v>
+        <v>-0.01044673054448334</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.1048384018101567</v>
+        <v>-0.004452376258378097</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU15" t="n">
         <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0.03022595117260291</v>
+        <v>-0.01195169058793689</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.06468790586757937</v>
+        <v>0.005750012481678813</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
         <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.08989740389370719</v>
+        <v>-0.03200110944715569</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED15" t="n">
         <v>0</v>
@@ -8801,10 +8801,10 @@
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0.008250936393093189</v>
+        <v>-0.0188335121015805</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.06591892135029737</v>
+        <v>0.02236591225194052</v>
       </c>
       <c r="EH15" t="n">
         <v>-0</v>
@@ -8813,10 +8813,10 @@
         <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0812537730863197</v>
+        <v>0.01010801904800389</v>
       </c>
       <c r="EK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL15" t="n">
         <v>-0</v>
@@ -8825,13 +8825,13 @@
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>-0.05475413324868535</v>
+        <v>-0.01411114583177563</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.03118346307603866</v>
+        <v>-0.005078543833339819</v>
       </c>
       <c r="EQ15" t="n">
         <v>0</v>
@@ -8840,61 +8840,61 @@
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.01163445658743485</v>
+        <v>0.008451738104563527</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
         <v>0</v>
       </c>
       <c r="EV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW15" t="n">
         <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.002219170222916915</v>
+        <v>-0.004403831271128907</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.04766320319669653</v>
+        <v>-0.007678068606787931</v>
       </c>
       <c r="EZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA15" t="n">
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.03010315613205233</v>
+        <v>0.01571078041628308</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.007314439201141072</v>
+        <v>0.0164561669528588</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0004657310381435379</v>
+        <v>-0.01333296487215776</v>
       </c>
       <c r="FI15" t="n">
         <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.1322291694523732</v>
+        <v>0.04528240228503843</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8909,10 +8909,10 @@
         <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>-0.07561915673084217</v>
+        <v>-0.02899383696252002</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.002271722556737243</v>
+        <v>0.03863396050649383</v>
       </c>
       <c r="FR15" t="n">
         <v>0</v>
@@ -8921,13 +8921,13 @@
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.06381162229372755</v>
+        <v>0.07101443972327409</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
         <v>0</v>
@@ -8936,25 +8936,25 @@
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0.06877409667588533</v>
+        <v>-0.004325889950437964</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.0174452672588998</v>
+        <v>0.01035262758181521</v>
       </c>
       <c r="GA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC15" t="n">
         <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
         <v>-0</v>
